--- a/docs/reports/Shelly_Waste_Shrink.xlsx
+++ b/docs/reports/Shelly_Waste_Shrink.xlsx
@@ -56848,7 +56848,7 @@
     <row r="6">
       <c r="C6" s="34" t="inlineStr">
         <is>
-          <t>Store: Demo Neighbourhood Store (Eden Terrace format).  Data to 25 Sep 2026.  Shelly v1.1.0.</t>
+          <t>Store: Demo Neighbourhood Store (Eden Terrace format).  Data to 25 Sep 2026.  Shelly v1.4.0.</t>
         </is>
       </c>
     </row>
@@ -56952,7 +56952,7 @@
     <row r="22">
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Generated by Shelly on 29 Sep 2026 22:17</t>
+          <t>Generated by Shelly on 03 Oct 2026 05:37</t>
         </is>
       </c>
     </row>

--- a/docs/reports/Shelly_Waste_Shrink.xlsx
+++ b/docs/reports/Shelly_Waste_Shrink.xlsx
@@ -56952,7 +56952,7 @@
     <row r="22">
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Generated by Shelly on 03 Oct 2026 05:37</t>
+          <t>Generated by Shelly on 03 Oct 2026 05:51</t>
         </is>
       </c>
     </row>
